--- a/从零开始学Slots/从零开始学Slots-02-基础篇-数值概念简介.xlsx
+++ b/从零开始学Slots/从零开始学Slots-02-基础篇-数值概念简介.xlsx
@@ -6624,6 +6624,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:I166" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -7029,5 +7032,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N51" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>